--- a/docentes/Moreno Aroyo Anél - Estadisticos 20212.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20212.xlsx
@@ -494,10 +494,10 @@
         <v>32</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>5</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>27</v>
@@ -506,7 +506,7 @@
         <v>84.38</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -585,7 +585,7 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -670,10 +670,10 @@
         <v>32</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>5</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>27</v>
@@ -682,7 +682,7 @@
         <v>84.38</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20212.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -68,6 +68,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>PATRICIO</t>
   </si>
 </sst>
 </file>
@@ -692,7 +701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -722,6 +731,29 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920197</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20212.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -70,10 +70,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
   </si>
   <si>
     <t>PATRICIO</t>
@@ -568,16 +577,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>71.88</v>
+      </c>
+      <c r="H2">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -591,16 +603,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>43.75</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +680,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,7 +706,7 @@
         <v>84.38</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -701,7 +716,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -733,16 +748,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920197</v>
+        <v>21330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -751,6 +766,29 @@
         <v>10</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920197</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20212.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -76,16 +76,25 @@
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>JORGE GUILLERMO</t>
   </si>
   <si>
     <t>PATRICIO</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
   </si>
 </sst>
 </file>
@@ -577,16 +586,16 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>71.88</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>9.800000000000001</v>
@@ -603,19 +612,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>43.75</v>
+        <v>84.38</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +689,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -706,7 +715,7 @@
         <v>84.38</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +725,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -754,10 +763,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -777,10 +786,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -790,6 +799,29 @@
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920203</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20212.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
   <si>
     <t>Mat</t>
   </si>
@@ -68,33 +68,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>PATRICIO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
   </si>
 </sst>
 </file>
@@ -689,7 +662,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -706,16 +679,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -725,7 +698,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -755,75 +728,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920190</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920197</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920203</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
